--- a/Team-Data/2012-13/4-13-2012-13.xlsx
+++ b/Team-Data/2012-13/4-13-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -775,7 +842,7 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.513</v>
+        <v>0.506</v>
       </c>
       <c r="H3" t="n">
         <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J3" t="n">
         <v>79.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L3" t="n">
         <v>6.1</v>
@@ -873,7 +940,7 @@
         <v>17.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.358</v>
+        <v>0.354</v>
       </c>
       <c r="O3" t="n">
         <v>16.4</v>
@@ -894,13 +961,13 @@
         <v>39.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>14.6</v>
       </c>
       <c r="W3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>4.5</v>
@@ -909,19 +976,19 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
         <v>19.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -951,7 +1018,7 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
         <v>19</v>
@@ -972,7 +1039,7 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
@@ -987,7 +1054,7 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
         <v>18</v>
@@ -996,7 +1063,7 @@
         <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>0.238</v>
+        <v>0.228</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1228,16 +1295,16 @@
         <v>81.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O5" t="n">
         <v>18.9</v>
@@ -1252,40 +1319,40 @@
         <v>11.3</v>
       </c>
       <c r="S5" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T5" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="U5" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V5" t="n">
         <v>14.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X5" t="n">
         <v>5.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Z5" t="n">
         <v>19.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB5" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1312,7 +1379,7 @@
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN5" t="n">
         <v>27</v>
@@ -1330,7 +1397,7 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT5" t="n">
         <v>27</v>
@@ -1339,7 +1406,7 @@
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1506,7 +1573,7 @@
         <v>20</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1703,7 +1770,7 @@
         <v>26</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>16</v>
@@ -1715,7 +1782,7 @@
         <v>28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
@@ -1879,7 +1946,7 @@
         <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>5</v>
@@ -1903,7 +1970,7 @@
         <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2274,7 @@
         <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2219,7 +2286,7 @@
         <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2622,7 +2689,7 @@
         <v>27</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>17</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
         <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.675</v>
+        <v>0.671</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2881,7 +2948,7 @@
         <v>16.5</v>
       </c>
       <c r="P14" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q14" t="n">
         <v>0.711</v>
@@ -2890,22 +2957,22 @@
         <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="V14" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W14" t="n">
         <v>9.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y14" t="n">
         <v>4.1</v>
@@ -2917,25 +2984,25 @@
         <v>21</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="AC14" t="n">
         <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>16</v>
@@ -2968,7 +3035,7 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT14" t="n">
         <v>18</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2995,7 +3062,7 @@
         <v>7</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3184,7 @@
         <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
         <v>54</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.675</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3239,22 +3306,22 @@
         <v>13.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O16" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P16" t="n">
         <v>21.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.773</v>
+        <v>0.775</v>
       </c>
       <c r="R16" t="n">
         <v>12.8</v>
       </c>
       <c r="S16" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T16" t="n">
         <v>42.5</v>
@@ -3281,22 +3348,22 @@
         <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>17</v>
@@ -3308,7 +3375,7 @@
         <v>18</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3326,7 +3393,7 @@
         <v>19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -3573,52 +3640,52 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" t="n">
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>0.463</v>
+        <v>0.468</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J18" t="n">
         <v>87.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O18" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P18" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R18" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T18" t="n">
         <v>43.9</v>
@@ -3645,13 +3712,13 @@
         <v>19.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>18</v>
@@ -3663,7 +3730,7 @@
         <v>18</v>
       </c>
       <c r="AH18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AI18" t="n">
         <v>6</v>
@@ -3681,7 +3748,7 @@
         <v>12</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -3755,64 +3822,64 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
         <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>0.375</v>
+        <v>0.367</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J19" t="n">
         <v>81.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L19" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M19" t="n">
         <v>17.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.305</v>
+        <v>0.304</v>
       </c>
       <c r="O19" t="n">
         <v>18.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.742</v>
+        <v>0.74</v>
       </c>
       <c r="R19" t="n">
         <v>12</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T19" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U19" t="n">
         <v>22.4</v>
       </c>
       <c r="V19" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W19" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X19" t="n">
         <v>4.8</v>
@@ -3821,19 +3888,19 @@
         <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
         <v>22.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
         <v>22</v>
@@ -3845,7 +3912,7 @@
         <v>22</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
@@ -3878,25 +3945,25 @@
         <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU19" t="n">
         <v>15</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>16</v>
       </c>
       <c r="AV19" t="n">
         <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
         <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ19" t="n">
         <v>6</v>
@@ -3908,7 +3975,7 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4094,7 @@
         <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>4.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>7</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="n">
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>0.25</v>
+        <v>0.253</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
@@ -4510,7 +4577,7 @@
         <v>6.3</v>
       </c>
       <c r="M23" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
         <v>0.332</v>
@@ -4522,13 +4589,13 @@
         <v>16.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R23" t="n">
         <v>10.8</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
         <v>42.8</v>
@@ -4537,10 +4604,10 @@
         <v>22.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W23" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X23" t="n">
         <v>4.4</v>
@@ -4549,7 +4616,7 @@
         <v>5.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA23" t="n">
         <v>16.4</v>
@@ -4558,10 +4625,10 @@
         <v>94.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4585,7 +4652,7 @@
         <v>19</v>
       </c>
       <c r="AL23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
         <v>18</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4761,19 +4828,19 @@
         <v>15</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
         <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4794,7 +4861,7 @@
         <v>19</v>
       </c>
       <c r="AU24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3</v>
+        <v>0.304</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4865,10 +4932,10 @@
         <v>37.2</v>
       </c>
       <c r="J25" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L25" t="n">
         <v>5.8</v>
@@ -4877,31 +4944,31 @@
         <v>17.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.331</v>
+        <v>0.329</v>
       </c>
       <c r="O25" t="n">
         <v>14.7</v>
       </c>
       <c r="P25" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q25" t="n">
         <v>0.744</v>
       </c>
       <c r="R25" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S25" t="n">
         <v>29.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V25" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W25" t="n">
         <v>8</v>
@@ -4922,19 +4989,19 @@
         <v>94.90000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH25" t="n">
         <v>17</v>
@@ -4943,7 +5010,7 @@
         <v>16</v>
       </c>
       <c r="AJ25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
         <v>23</v>
@@ -4961,7 +5028,7 @@
         <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ25" t="n">
         <v>20</v>
@@ -4976,7 +5043,7 @@
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5334,7 +5401,7 @@
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT27" t="n">
         <v>26</v>
@@ -5343,7 +5410,7 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5528,7 +5595,7 @@
         <v>18</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5674,7 +5741,7 @@
         <v>16</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>15</v>
@@ -5713,7 +5780,7 @@
         <v>19</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5929,7 @@
         <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN30" t="n">
         <v>8</v>
@@ -5874,7 +5941,7 @@
         <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
@@ -5886,7 +5953,7 @@
         <v>16</v>
       </c>
       <c r="AU30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV30" t="n">
         <v>19</v>
@@ -5910,7 +5977,7 @@
         <v>13</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="AE31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF31" t="n">
         <v>23</v>
@@ -6086,13 +6153,13 @@
         <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>27</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-13-2012-13</t>
+          <t>2013-04-13</t>
         </is>
       </c>
     </row>
